--- a/data/merged/2026-09-28/MERGED_ES_Mite-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_ES_Mite-Vacuum_2026-09-28.xlsx
@@ -4582,13 +4582,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4649,50 +4649,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId30" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Product 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId31" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5034,7 +4990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR32"/>
+  <dimension ref="A1:BR31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -9766,61 +9722,53 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0FBX24WH6</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Color: Morado</t>
-        </is>
-      </c>
+          <t>B0FDWVV95V</t>
+        </is>
+      </c>
+      <c r="D23" s="14"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Marca: syayw | Función especial: Inalámbrico | ¿Es inalámbrico?: Sí | Capacidad: 185 ml | Usos recomendados para el producto: Limpieza profunda de cojines, sofás, hojas, tela, ropa de cama y superficies; eliminación de pelo de mascotas | Factor de forma: De mano | Color: Morado | Nombre del modelo: syayw-SQ9687FVEBHB003E | Dimensiones del producto: 26,9l. x 25,2an. x 14,3al. centímetros | Fabricante: syayw</t>
+          <t>Marca: JIGOO | Función especial: Hipoalergénica | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Tapicería, Alfombra | Fuente de alimentación: Batería | Componentes incluidos: Cepillo para limpiar el polvo, Herramienta para hendiduras | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: colchones y tapicería | Factor de forma: De mano | Color: Verde</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>syayw</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=syayw</t>
+          <t>https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Limpiador Varuum – 68 W Fuerte Cama vacío para Limpieza Profunda | Eliminador de para Mascotas vacío para Cojines de sofá Hojas Tela Ropa de Cama Superficies</t>
+          <t>JIGOO T600 T600 - Tetina antiácaros/Floral Delight (aceite esencial de plantas)</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>Prevención avanzada del polvo: el uso de acumulación y propagación de polvo de tecnología avanzada, el vacío BED sin cama garantiza que su hogar esté seguro cada vez que lo use
-Filtración avanzada: con un sistema de filtración avanzado, nuestro vacío puede aislar eficazmente los desechos grandes y capturar incluso las partículas más pequeñas para una limpieza profunda para garantizar el máximo saneamiento
-Funcionalidad eficiente: aprovechando la potencia de 10 kPa y la tecnología eficiente, este vacío puede proporcionar un rendimiento confiable y duradero para la limpieza profunda y durabilidad de su
-Portátil de usar: diseño compacto y ligero, inalámbrico, lo hace flexible y fácil de usar para garantizar la limpieza sin esfuerzo de colchones y otras superficies
-Fácil limpieza: con nuestro vacío podrás disfrutar fácilmente con un filtro de alta eficiencia que se puede enjuagar fácilmente con agua. Mantiene su dispositivo a menudo eficaz e higiénico, a menudo</t>
+          <t>JIGOO T600 - Aspirador antiácaros para colchones: Floral Delight (aceite esencial de plantas)</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FBX24WH6?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FDWVV95V?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0FQ4FRYT7</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="M23" s="14" t="inlineStr">
         <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de mano</t>
+          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
         </is>
       </c>
       <c r="N23" s="14" t="inlineStr">
@@ -9829,7 +9777,7 @@
         </is>
       </c>
       <c r="O23" s="15">
-        <v>1559184</v>
+        <v>544989</v>
       </c>
       <c r="P23" s="15"/>
       <c r="Q23" s="16">
@@ -9837,14 +9785,12 @@
       </c>
       <c r="R23" s="17" t="inlineStr">
         <is>
-          <t>Aspiradoras de futones
-Aspiradoras de mano</t>
+          <t>Aspiradoras de futones</t>
         </is>
       </c>
       <c r="S23" s="18" t="inlineStr">
         <is>
-          <t>31
-1852</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T23" s="15"/>
@@ -9855,33 +9801,27 @@
       <c r="Y23" s="19">
         <v>1</v>
       </c>
-      <c r="Z23" s="20">
-        <v>38.11</v>
-      </c>
+      <c r="Z23" s="20"/>
       <c r="AA23" s="4"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="2"/>
-      <c r="AD23" s="19"/>
+      <c r="AD23" s="19">
+        <v>11</v>
+      </c>
       <c r="AE23" s="15"/>
-      <c r="AF23" s="21"/>
+      <c r="AF23" s="21">
+        <v>4.2</v>
+      </c>
       <c r="AG23" s="22">
         <v>0</v>
       </c>
-      <c r="AH23" s="20">
-        <v>5.05</v>
-      </c>
+      <c r="AH23" s="20"/>
       <c r="AI23" s="16">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AJ23"/>
-      <c r="AK23" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AL23" s="19">
-        <v>299</v>
-      </c>
+      <c r="AK23" s="13"/>
+      <c r="AL23" s="19"/>
       <c r="AM23" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -9890,94 +9830,46 @@
       <c r="AN23" s="13"/>
       <c r="AO23" s="13"/>
       <c r="AP23" s="20"/>
-      <c r="AQ23" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR23" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS23" s="14" t="inlineStr">
-        <is>
-          <t>nousaeg</t>
-        </is>
-      </c>
+      <c r="AQ23" s="19"/>
+      <c r="AR23" s="19"/>
+      <c r="AS23" s="14"/>
       <c r="AT23" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU23" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV23" s="14" t="inlineStr">
-        <is>
-          <t>蚌埠市 蚌山区 安徽 233000 CN</t>
-        </is>
-      </c>
-      <c r="AW23" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3T9BSXCSWI46M</t>
-        </is>
-      </c>
+      <c r="AU23" s="13"/>
+      <c r="AV23" s="14"/>
+      <c r="AW23" s="13"/>
       <c r="AX23" s="13"/>
       <c r="AY23" s="13"/>
       <c r="AZ23" s="13"/>
       <c r="BA23" s="13"/>
       <c r="BB23" s="13"/>
-      <c r="BC23" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC23" s="13"/>
       <c r="BD23" s="13"/>
       <c r="BE23" s="13"/>
-      <c r="BF23" s="13"/>
+      <c r="BF23" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG23" s="13"/>
       <c r="BH23" s="14"/>
       <c r="BI23" s="23"/>
-      <c r="BJ23" s="23" t="inlineStr">
-        <is>
-          <t>1,02 kg</t>
-        </is>
-      </c>
-      <c r="BK23" s="23" t="inlineStr">
-        <is>
-          <t>1.02 kg</t>
-        </is>
-      </c>
+      <c r="BJ23" s="23"/>
+      <c r="BK23" s="23"/>
       <c r="BL23" s="23" t="inlineStr">
         <is>
-          <t>26,9l. x 25,2an. x 14,3al. centímetros</t>
+          <t>6l. x 1,3an. x 8al. centímetros</t>
         </is>
       </c>
       <c r="BM23" s="23"/>
-      <c r="BN23" s="23" t="inlineStr">
-        <is>
-          <t>1.02 kg</t>
-        </is>
-      </c>
-      <c r="BO23" s="23" t="inlineStr">
-        <is>
-          <t>1.02 kg</t>
-        </is>
-      </c>
-      <c r="BP23" s="23" t="inlineStr">
-        <is>
-          <t>26.9 x 25.2 x 14.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ23" s="23" t="inlineStr">
-        <is>
-          <t>26.90 x 25.20 x 14.30 cm</t>
-        </is>
-      </c>
-      <c r="BR23" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BN23" s="23"/>
+      <c r="BO23" s="23"/>
+      <c r="BP23" s="23"/>
+      <c r="BQ23" s="23"/>
+      <c r="BR23" s="13"/>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
@@ -9986,48 +9878,52 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Marca: JIGOO | Función especial: Hipoalergénica | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Tapicería, Alfombra | Fuente de alimentación: Batería | Componentes incluidos: Cepillo para limpiar el polvo, Herramienta para hendiduras | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: colchones y tapicería | Factor de forma: De mano | Color: Verde</t>
+          <t>Marca: Yaasier | Función especial: Portátil | Tipo de filtro: Filtro HEPA | Recomendación de superficie: nan | Fuente de alimentación: Batería | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: Superficies de tela, eliminación de pelo de animales, entornos silenciosos | Factor de forma: De mano | Color: Blanco | Dimensiones del producto: 40l. x 40an. x 80al. milímetros</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 T600 - Tetina antiácaros/Floral Delight (aceite esencial de plantas)</t>
+          <t>Yaasier Aspirador de Ácaros, Mini Aspirador Antiácaros para Colchones con Luz UV, Aspiradora de Mano con Filtro HEPA para Colchones, Camas, Sofás de Tela, Almohadas, Alfombras</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 - Aspirador antiácaros para colchones: Floral Delight (aceite esencial de plantas)</t>
+          <t>Ligero y compacto: el aspirador de cama toma tres en una sola función de flotación de alta frecuencia, fuerte succión y luz violeta penetrante. Almohadilla de pulsación doble Beat, luz púrpura de 253,7 nm, área de limpieza más grande, mayor eficiencia de limpieza.
+Diseño ligero e inalámbrico: disfruta de la libertad de limpieza inalámbrica. La batería recargable ofrece una larga duración de 30 minutos. Nuestra aspiradora es una de las más ligeras del mercado, lo que hace que sea más fácil de usar y menos exigido sus músculos y articulaciones. Nuestro diseño elegante y moderno se adapta a tu estética y a tu hogar.
+Sistema de filtración muy eficiente: la aspiradora de colchón utiliza un filtro HEPA reutilizable y lavable en profundidad en combinación con un tejido filtrante de acero inoxidable que podría recoger aproximadamente el 99,97% de partículas tan pequeñas como 0,3 micras, y aislar las partículas grandes de los residuos, bloqueando firmemente el polvo y la suciedad, y no goteará.
+【Caja de polvo lavable】 Máquina de limpieza de colchones Snap-on, fácil de limpiar, se puede limpiar directamente debajo del grifo, limpieza regular sin la molestia de succión debilitada o polvo obstruido. Nota: el filtro debe usarse después del secado.
+【Ámbito de aplicación】El aspirador de cama puede aspirar fácilmente el pelo de animales y la caspa, etc. Adecuado para superficies de tela: colchones, sábanas, almohadas, alfombras, sofás de tela, etc. El diseño de cancelación de ruido no molestará a los bebés o mascotas dormidos.</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FKRC3KQY?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -10041,7 +9937,7 @@
         </is>
       </c>
       <c r="O24" s="15">
-        <v>544989</v>
+        <v>517067</v>
       </c>
       <c r="P24" s="15"/>
       <c r="Q24" s="16">
@@ -10054,7 +9950,7 @@
       </c>
       <c r="S24" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T24" s="15"/>
@@ -10070,11 +9966,11 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE24" s="15"/>
       <c r="AF24" s="21">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
@@ -10110,14 +10006,14 @@
       <c r="AZ24" s="13"/>
       <c r="BA24" s="13"/>
       <c r="BB24" s="13"/>
-      <c r="BC24" s="13"/>
+      <c r="BC24" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD24" s="13"/>
       <c r="BE24" s="13"/>
-      <c r="BF24" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF24" s="13"/>
       <c r="BG24" s="13"/>
       <c r="BH24" s="14"/>
       <c r="BI24" s="23"/>
@@ -10125,7 +10021,7 @@
       <c r="BK24" s="23"/>
       <c r="BL24" s="23" t="inlineStr">
         <is>
-          <t>6l. x 1,3an. x 8al. centímetros</t>
+          <t>40l. x 40an. x 80al. milímetros</t>
         </is>
       </c>
       <c r="BM24" s="23"/>
@@ -10142,52 +10038,53 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Marca: Yaasier | Función especial: Portátil | Tipo de filtro: Filtro HEPA | Recomendación de superficie: nan | Fuente de alimentación: Batería | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: Superficies de tela, eliminación de pelo de animales, entornos silenciosos | Factor de forma: De mano | Color: Blanco | Dimensiones del producto: 40l. x 40an. x 80al. milímetros</t>
+          <t>Marca: Teant | Voltaje: 230 Voltios | Componentes incluidos: Cepillo giratorio con parada automática, Cepillo antienredos | ¿Es inalámbrico?: No | Peso del producto: 1,9 Kilogramos | Factor de forma: De mano | Color: Blanco | Nombre del modelo: MV-GREY</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirador de Ácaros, Mini Aspirador Antiácaros para Colchones con Luz UV, Aspiradora de Mano con Filtro HEPA para Colchones, Camas, Sofás de Tela, Almohadas, Alfombras</t>
+          <t>Mayking Teant Aspiradora para Colchones 2 Velocidades (14 kPa/18 kPa)</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>Ligero y compacto: el aspirador de cama toma tres en una sola función de flotación de alta frecuencia, fuerte succión y luz violeta penetrante. Almohadilla de pulsación doble Beat, luz púrpura de 253,7 nm, área de limpieza más grande, mayor eficiencia de limpieza.
-Diseño ligero e inalámbrico: disfruta de la libertad de limpieza inalámbrica. La batería recargable ofrece una larga duración de 30 minutos. Nuestra aspiradora es una de las más ligeras del mercado, lo que hace que sea más fácil de usar y menos exigido sus músculos y articulaciones. Nuestro diseño elegante y moderno se adapta a tu estética y a tu hogar.
-Sistema de filtración muy eficiente: la aspiradora de colchón utiliza un filtro HEPA reutilizable y lavable en profundidad en combinación con un tejido filtrante de acero inoxidable que podría recoger aproximadamente el 99,97% de partículas tan pequeñas como 0,3 micras, y aislar las partículas grandes de los residuos, bloqueando firmemente el polvo y la suciedad, y no goteará.
-【Caja de polvo lavable】 Máquina de limpieza de colchones Snap-on, fácil de limpiar, se puede limpiar directamente debajo del grifo, limpieza regular sin la molestia de succión debilitada o polvo obstruido. Nota: el filtro debe usarse después del secado.
-【Ámbito de aplicación】El aspirador de cama puede aspirar fácilmente el pelo de animales y la caspa, etc. Adecuado para superficies de tela: colchones, sábanas, almohadas, alfombras, sofás de tela, etc. El diseño de cancelación de ruido no molestará a los bebés o mascotas dormidos.</t>
+          <t>[Limpieza profunda y potente con 2 Velocidades] El Aspiradora para Colchones antiacaros Teant ofrece 2 niveles de succión ajustables hasta 18 kPa, mientras que el motor Hyper Helix proporciona 33 000 rpm de potentes golpes para penetrar en colchones, sofás y tejidos, levantando el polvo, la caspa y los alérgenos. Los contenedores dobles para el polvo y el filtro HEPA capturan el 99,97 % de las micropartículas (de hasta 0,3 µm) y separan los pelos para evitar obstrucciones, manteniendo una potente succión para una limpieza más profunda y uniforme y un espacio de descanso más fresco
+[Detección con luz verde, no se Esconde el Polvo] El aspirador portátil inteligente para colchones utiliza luz verde de 555 nm y tecnología de lente para detectar el polvo oculto, los pelos de animales y las micropartículas en colchones oscuros, sofás y hendiduras profundas de los tejidos, sin dejar ningún punto sin limpiar. El cable extralargo de 5 metros llega a todos los rincones de una cama king size sin tener que desconectarlo, para una limpieza más fácil, inteligente y profunda
+[Pantalla LED Multifunción para una Limpieza Visible] Los LED inteligentes con indicadores dinámicos rojos y azules muestran el progreso de la limpieza en tiempo real. La amplia y clara pantalla LED del aspirador Antiacaro de cama permite supervisar al instante las funciones: Golpes, Calor, UV-C, Ultrasonidos y Aniones. (Consejo: un color rojo prolongado puede indicar que el sensor de polvo está cubierto; límpielo con un paño limpio y húmedo)
+[Apunta a las Micropartículas Ocultas, protege a tu Familia] La luz UV-C de 253,7 nm, combinada con tecnología ultrasónica de 40 000 Hz, permite que el Aspirador de Mano Teant penetre profundamente en las fibras del colchón para detectar y eliminar el 99,9 % de las partículas invisibles. Los rodillos dobles con sensor de gravedad activan los rayos UV solo después de que ambas ruedas hayan estado en contacto con la superficie durante 2 segundos y se apagan si se levantan, lo que evita pérdidas de luz y mantiene a tu familia segura
+[Aire Caliente, Aroma y Iones negativos para un hogar Fresco] Despídase de las camas húmedas y los malos olores. El aspirador para colchones Teant proporciona un flujo de aire calentado a 65 °C para secar eficazmente los tejidos: disfrute de un colchón limpio y seco. La tecnología de iones negativos ayuda a neutralizar las partículas en suspensión en el aire y a refrescarlo, mientras que la pastilla aromática elimina los olores y añade una delicada fragancia natural, perfecta para una noche de sueño limpia y acogedora
+[Doble Protección: Cepillo Antienredos y Protección Contra Sobrecalentamiento] El aspirador de colchones Teant cuenta con un cepillo giratorio con parada automática que se detiene al instante en caso de enredos, protegiendo el motor y prolongando su vida útil. La protección contra sobrecalentamiento incorporada interrumpe automáticamente el funcionamiento tras un uso prolongado. Basta con apagarlo, dejarlo enfriar durante 2 horas y luego reanudar la limpieza con seguridad</t>
         </is>
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FKRC3KQY?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FN3GPQZM?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41B+I610d+L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
@@ -10201,7 +10098,7 @@
         </is>
       </c>
       <c r="O25" s="15">
-        <v>517067</v>
+        <v>788744</v>
       </c>
       <c r="P25" s="15"/>
       <c r="Q25" s="16">
@@ -10214,7 +10111,7 @@
       </c>
       <c r="S25" s="18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T25" s="15"/>
@@ -10230,11 +10127,11 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AE25" s="15"/>
       <c r="AF25" s="21">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -10277,17 +10174,25 @@
       </c>
       <c r="BD25" s="13"/>
       <c r="BE25" s="13"/>
-      <c r="BF25" s="13"/>
+      <c r="BF25" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG25" s="13"/>
       <c r="BH25" s="14"/>
       <c r="BI25" s="23"/>
-      <c r="BJ25" s="23"/>
-      <c r="BK25" s="23"/>
-      <c r="BL25" s="23" t="inlineStr">
-        <is>
-          <t>40l. x 40an. x 80al. milímetros</t>
-        </is>
-      </c>
+      <c r="BJ25" s="23" t="inlineStr">
+        <is>
+          <t>1,9 Kilogramos</t>
+        </is>
+      </c>
+      <c r="BK25" s="23" t="inlineStr">
+        <is>
+          <t>1.90 kg</t>
+        </is>
+      </c>
+      <c r="BL25" s="23"/>
       <c r="BM25" s="23"/>
       <c r="BN25" s="23"/>
       <c r="BO25" s="23"/>
@@ -10302,53 +10207,52 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Marca: Teant | Voltaje: 230 Voltios | Componentes incluidos: Cepillo giratorio con parada automática, Cepillo antienredos | ¿Es inalámbrico?: No | Peso del producto: 1,9 Kilogramos | Factor de forma: De mano | Color: Blanco | Nombre del modelo: MV-GREY</t>
+          <t>Marca: Yaasier | Función especial: Portátil | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Colchones, ropa de cama, almohada, alfombras, sofás de tela | Fuente de alimentación: Batería | Componentes incluidos: Aspirador de Ácaros | ¿Es inalámbrico?: Sí | Peso del producto: 250 Gramos | Usos recomendados para el producto: Colchones, sábanas, almohadas, alfombras, sofás de tela, pelo de mascotas | Factor de forma: De mano</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Mayking Teant Aspiradora para Colchones 2 Velocidades (14 kPa/18 kPa)</t>
+          <t>Yaasier Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para colchones, sofás, Almohadas, alfombras</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>[Limpieza profunda y potente con 2 Velocidades] El Aspiradora para Colchones antiacaros Teant ofrece 2 niveles de succión ajustables hasta 18 kPa, mientras que el motor Hyper Helix proporciona 33 000 rpm de potentes golpes para penetrar en colchones, sofás y tejidos, levantando el polvo, la caspa y los alérgenos. Los contenedores dobles para el polvo y el filtro HEPA capturan el 99,97 % de las micropartículas (de hasta 0,3 µm) y separan los pelos para evitar obstrucciones, manteniendo una potente succión para una limpieza más profunda y uniforme y un espacio de descanso más fresco
-[Detección con luz verde, no se Esconde el Polvo] El aspirador portátil inteligente para colchones utiliza luz verde de 555 nm y tecnología de lente para detectar el polvo oculto, los pelos de animales y las micropartículas en colchones oscuros, sofás y hendiduras profundas de los tejidos, sin dejar ningún punto sin limpiar. El cable extralargo de 5 metros llega a todos los rincones de una cama king size sin tener que desconectarlo, para una limpieza más fácil, inteligente y profunda
-[Pantalla LED Multifunción para una Limpieza Visible] Los LED inteligentes con indicadores dinámicos rojos y azules muestran el progreso de la limpieza en tiempo real. La amplia y clara pantalla LED del aspirador Antiacaro de cama permite supervisar al instante las funciones: Golpes, Calor, UV-C, Ultrasonidos y Aniones. (Consejo: un color rojo prolongado puede indicar que el sensor de polvo está cubierto; límpielo con un paño limpio y húmedo)
-[Apunta a las Micropartículas Ocultas, protege a tu Familia] La luz UV-C de 253,7 nm, combinada con tecnología ultrasónica de 40 000 Hz, permite que el Aspirador de Mano Teant penetre profundamente en las fibras del colchón para detectar y eliminar el 99,9 % de las partículas invisibles. Los rodillos dobles con sensor de gravedad activan los rayos UV solo después de que ambas ruedas hayan estado en contacto con la superficie durante 2 segundos y se apagan si se levantan, lo que evita pérdidas de luz y mantiene a tu familia segura
-[Aire Caliente, Aroma y Iones negativos para un hogar Fresco] Despídase de las camas húmedas y los malos olores. El aspirador para colchones Teant proporciona un flujo de aire calentado a 65 °C para secar eficazmente los tejidos: disfrute de un colchón limpio y seco. La tecnología de iones negativos ayuda a neutralizar las partículas en suspensión en el aire y a refrescarlo, mientras que la pastilla aromática elimina los olores y añade una delicada fragancia natural, perfecta para una noche de sueño limpia y acogedora
-[Doble Protección: Cepillo Antienredos y Protección Contra Sobrecalentamiento] El aspirador de colchones Teant cuenta con un cepillo giratorio con parada automática que se detiene al instante en caso de enredos, protegiendo el motor y prolongando su vida útil. La protección contra sobrecalentamiento incorporada interrumpe automáticamente el funcionamiento tras un uso prolongado. Basta con apagarlo, dejarlo enfriar durante 2 horas y luego reanudar la limpieza con seguridad</t>
+          <t>[Tecnología avanzada tres en uno] Equipado con una almohadilla de pulso de doble ritmo y una luz UV de 253,7 nm, esta aspiradora ofrece una gran área de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de sus colchones y textiles.
+[Diseño inalámbrico ligero] Maximice su comodidad con esta aspiradora inalámbrica ligera que tiene una batería recargable que ofrece hasta 30 minutos de tiempo de funcionamiento. Su diseño moderno y elegante se adapta perfectamente a cualquier decoración de interiores y hace que la limpieza sea fácil.
+[Sistema de filtración de alta eficiencia] Limpiador de colchones con un filtro HEPA lavable y un filtro de algodón en la salida, esta aspiradora atrapa el 99,97 % de las partículas de polvo fino, proporciona un aire más saludable y reduce la contaminación secundaria, ideal para personas sensibles y familias con niños.
+[Fácil de limpiar y lavable] Aspirador de ácaros con el depósito de polvo lavable con agua corriente hace que su aspiradora sea más fácil de limpiar. Seque el filtro antes de reutilizarlo para garantizar una succión óptima y un rendimiento de limpieza constante
+[Versatilidad y comodidad de uso] Aspirador de ácaros con luz UV Ideal para aspirar el pelo de animales y la caspa en diferentes superficies de tela como colchones, cojines, sofás y alfombras. Disfruta de una limpieza silenciosa que no molesta a bebés o mascotas dormidos</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FN3GPQZM?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FVS559GZ?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41B+I610d+L._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0GHDFVK7R</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -10362,7 +10266,7 @@
         </is>
       </c>
       <c r="O26" s="15">
-        <v>788744</v>
+        <v>340911</v>
       </c>
       <c r="P26" s="15"/>
       <c r="Q26" s="16">
@@ -10375,7 +10279,7 @@
       </c>
       <c r="S26" s="18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T26" s="15"/>
@@ -10391,11 +10295,11 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AE26" s="15"/>
       <c r="AF26" s="21">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -10436,27 +10340,31 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD26" s="13"/>
+      <c r="BD26" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE26" s="13"/>
-      <c r="BF26" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF26" s="13"/>
       <c r="BG26" s="13"/>
       <c r="BH26" s="14"/>
       <c r="BI26" s="23"/>
       <c r="BJ26" s="23" t="inlineStr">
         <is>
-          <t>1,9 Kilogramos</t>
+          <t>250 Gramos</t>
         </is>
       </c>
       <c r="BK26" s="23" t="inlineStr">
         <is>
-          <t>1.90 kg</t>
-        </is>
-      </c>
-      <c r="BL26" s="23"/>
+          <t>250.00 g</t>
+        </is>
+      </c>
+      <c r="BL26" s="23" t="inlineStr">
+        <is>
+          <t>6l. x 4an. x 8al. centímetros</t>
+        </is>
+      </c>
       <c r="BM26" s="23"/>
       <c r="BN26" s="23"/>
       <c r="BO26" s="23"/>
@@ -10471,13 +10379,13 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Marca: Yaasier | Función especial: Portátil | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Colchones, ropa de cama, almohada, alfombras, sofás de tela | Fuente de alimentación: Batería | Componentes incluidos: Aspirador de Ácaros | ¿Es inalámbrico?: Sí | Peso del producto: 250 Gramos | Usos recomendados para el producto: Colchones, sábanas, almohadas, alfombras, sofás de tela, pelo de mascotas | Factor de forma: De mano</t>
+          <t>Marca: Yaasier | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Alfombra, Relleno | Fuente de alimentación: Batería | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: colchones, sofás, textiles, eliminar el pelo de animales, reducción de alérgenos | Factor de forma: De mano | Color: Blanco | Nombre del modelo: 1X1BSCMY | Dimensiones del producto: 6l. x 4an. x 8al. centímetros</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
@@ -10492,21 +10400,21 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para colchones, sofás, Almohadas, alfombras</t>
+          <t>Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para colchones, sofás, Almohadas, alfombras</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>[Tecnología avanzada tres en uno] Equipado con una almohadilla de pulso de doble ritmo y una luz UV de 253,7 nm, esta aspiradora ofrece una gran área de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de sus colchones y textiles.
+          <t>[Tecnología avanzada tres en uno] Aspiradora antiácaros equipada [Tecnología avanzada tres en uno] Equipado con una almohadilla de pulso de doble ritmo y luz UV de 253,7 nm, esta aspiradora ofrece un amplio rango de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de sus colchones y textiles. Con una almohadilla de pulso de doble ritmo y 253,7 nm. Esta aspiradora ofrece luz ultravioleta. una amplia zona de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de tus colchones y textiles.
 [Diseño inalámbrico ligero] Maximice su comodidad con esta aspiradora inalámbrica ligera que tiene una batería recargable que ofrece hasta 30 minutos de tiempo de funcionamiento. Su diseño moderno y elegante se adapta perfectamente a cualquier decoración de interiores y hace que la limpieza sea fácil.
 [Sistema de filtración de alta eficiencia] Limpiador de colchones con un filtro HEPA lavable y un filtro de algodón en la salida, esta aspiradora atrapa el 99,97 % de las partículas de polvo fino, proporciona un aire más saludable y reduce la contaminación secundaria, ideal para personas sensibles y familias con niños.
-[Fácil de limpiar y lavable] Aspirador de ácaros con el depósito de polvo lavable con agua corriente hace que su aspiradora sea más fácil de limpiar. Seque el filtro antes de reutilizarlo para garantizar una succión óptima y un rendimiento de limpieza constante
-[Versatilidad y comodidad de uso] Aspirador de ácaros con luz UV Ideal para aspirar el pelo de animales y la caspa en diferentes superficies de tela como colchones, cojines, sofás y alfombras. Disfruta de una limpieza silenciosa que no molesta a bebés o mascotas dormidos</t>
+[Fácil de limpiar y lavable] Aspirador de ácaros con el depósito de polvo lavable con agua corriente hace que su aspiradora sea más fácil de limpiar. Seque el filtro antes de reutilizarlo para garantizar una succión óptima y un rendimiento de limpieza constante.
+[Versatilidad y comodidad de uso] Aspirador de ácaros con luz UV Ideal para aspirar el pelo de animales y la caspa en diferentes superficies de tela como colchones, cojines, sofás y alfombras. Disfruta de una limpieza silenciosa que no molesta a bebés o mascotas dormidos.</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FVS559GZ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
@@ -10516,7 +10424,7 @@
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0GHDFVK7R</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -10530,7 +10438,7 @@
         </is>
       </c>
       <c r="O27" s="15">
-        <v>340911</v>
+        <v>1158454</v>
       </c>
       <c r="P27" s="15"/>
       <c r="Q27" s="16">
@@ -10543,7 +10451,7 @@
       </c>
       <c r="S27" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T27" s="15"/>
@@ -10559,11 +10467,11 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="19">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AE27" s="15"/>
       <c r="AF27" s="21">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -10604,26 +10512,14 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD27" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD27" s="13"/>
       <c r="BE27" s="13"/>
       <c r="BF27" s="13"/>
       <c r="BG27" s="13"/>
       <c r="BH27" s="14"/>
       <c r="BI27" s="23"/>
-      <c r="BJ27" s="23" t="inlineStr">
-        <is>
-          <t>250 Gramos</t>
-        </is>
-      </c>
-      <c r="BK27" s="23" t="inlineStr">
-        <is>
-          <t>250.00 g</t>
-        </is>
-      </c>
+      <c r="BJ27" s="23"/>
+      <c r="BK27" s="23"/>
       <c r="BL27" s="23" t="inlineStr">
         <is>
           <t>6l. x 4an. x 8al. centímetros</t>
@@ -10643,52 +10539,56 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
-        </is>
-      </c>
-      <c r="D28" s="14"/>
+          <t>B0G4RSJQVT</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Color: Gris Oscuro | Tamaño: 500W</t>
+        </is>
+      </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Marca: Yaasier | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Alfombra, Relleno | Fuente de alimentación: Batería | ¿Es inalámbrico?: Sí | Usos recomendados para el producto: colchones, sofás, textiles, eliminar el pelo de animales, reducción de alérgenos | Factor de forma: De mano | Color: Blanco | Nombre del modelo: 1X1BSCMY | Dimensiones del producto: 6l. x 4an. x 8al. centímetros</t>
+          <t>Marca: Lubluelu | Función especial: Luz UV | Tipo de filtro: Cartucho | Recomendación de superficie: Alfombra | Fuente de alimentación: Eléctrico con cable | Componentes incluidos: Rodillo de cepillo | ¿Es inalámbrico?: No | Succión máxima: 18000 Milímetros | Usos recomendados para el producto: Colchones, sofás, alfombras, ropa de cama, juguetes de peluche, pelo de mascota | Factor de forma: De mano</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.es/stores/Lubluelu/page/6949B717-1950-436B-B468-8BFB57AEF209?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para colchones, sofás, Almohadas, alfombras</t>
+          <t>Lubluelu Aspirador de ácaros 3 en 1 para colchones, 18 KPa fuerte potencia de succión, limpiador de colchones contra ácaros, polvo y alérgenos, aspiradora de mano para cama, sofá, tapicería y textiles</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>[Tecnología avanzada tres en uno] Aspiradora antiácaros equipada [Tecnología avanzada tres en uno] Equipado con una almohadilla de pulso de doble ritmo y luz UV de 253,7 nm, esta aspiradora ofrece un amplio rango de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de sus colchones y textiles. Con una almohadilla de pulso de doble ritmo y 253,7 nm. Esta aspiradora ofrece luz ultravioleta. una amplia zona de limpieza y una mayor eficiencia, ideal para eliminar los ácaros del polvo y otros alérgenos de tus colchones y textiles.
-[Diseño inalámbrico ligero] Maximice su comodidad con esta aspiradora inalámbrica ligera que tiene una batería recargable que ofrece hasta 30 minutos de tiempo de funcionamiento. Su diseño moderno y elegante se adapta perfectamente a cualquier decoración de interiores y hace que la limpieza sea fácil.
-[Sistema de filtración de alta eficiencia] Limpiador de colchones con un filtro HEPA lavable y un filtro de algodón en la salida, esta aspiradora atrapa el 99,97 % de las partículas de polvo fino, proporciona un aire más saludable y reduce la contaminación secundaria, ideal para personas sensibles y familias con niños.
-[Fácil de limpiar y lavable] Aspirador de ácaros con el depósito de polvo lavable con agua corriente hace que su aspiradora sea más fácil de limpiar. Seque el filtro antes de reutilizarlo para garantizar una succión óptima y un rendimiento de limpieza constante.
-[Versatilidad y comodidad de uso] Aspirador de ácaros con luz UV Ideal para aspirar el pelo de animales y la caspa en diferentes superficies de tela como colchones, cojines, sofás y alfombras. Disfruta de una limpieza silenciosa que no molesta a bebés o mascotas dormidos.</t>
+          <t>Fuerte succión de 18 KPa para una limpieza profunda: potente aspiradora elimina instantáneamente el polvo, la suciedad y los ácaros del polvo de los colchones, sofás, alfombras, ropa de cama y peluches. Proporciona una limpieza profunda en cada esquina.
+Limpieza profunda multietapa de ácaros y alérgenos: combinación de rodillo de cepillo, vibración ultrasónica y calentamiento a alta temperatura, elimina eficazmente los ácaros y alérgenos profundamente en los tejidos, dejando un hogar fresco e higiénico.
+Limpieza hipoalergénica y suave: diseñada para hogares sensibles, la limpieza profunda se basa en tecnología mecánica de golpes y calor en lugar de aditivos químicos. Ideal para personas alérgicas, habitaciones infantiles y familias con mascotas, mientras que los textiles y las superficies se cuidan de manera cuidadosa con el material.
+Versátil para diferentes superficies y usos: adecuado para colchones, sofás, alfombras, ropa de cama y juguetes de peluche. Disuelve el polvo y las partículas de tejidos profundos y ayuda a mantener las zonas de vida muy utilizadas. Ideal para dormitorios, salas de estar y hogares con mascotas, para un hogar higiénico.
+Práctico y fácil de usar en el día a día: cable extralargo de 4 m para un mayor alcance, diseño compacto y ligero para un manejo flexible para la limpieza de colchones y muebles tapizados, así como un mantenimiento sencillo. El depósito de polvo se puede vaciar rápidamente y dejar que el filtro se seque al aire después de la limpieza.</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.es/dp/B0G4RSJQVT?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0HJRMXSZC</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -10702,7 +10602,7 @@
         </is>
       </c>
       <c r="O28" s="15">
-        <v>1158454</v>
+        <v>1050716</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="16">
@@ -10715,7 +10615,7 @@
       </c>
       <c r="S28" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T28" s="15"/>
@@ -10731,11 +10631,11 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AE28" s="15"/>
       <c r="AF28" s="21">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -10771,11 +10671,7 @@
       <c r="AZ28" s="13"/>
       <c r="BA28" s="13"/>
       <c r="BB28" s="13"/>
-      <c r="BC28" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC28" s="13"/>
       <c r="BD28" s="13"/>
       <c r="BE28" s="13"/>
       <c r="BF28" s="13"/>
@@ -10786,7 +10682,7 @@
       <c r="BK28" s="23"/>
       <c r="BL28" s="23" t="inlineStr">
         <is>
-          <t>6l. x 4an. x 8al. centímetros</t>
+          <t>26,5l. x 25,5an. x 33,5al. centímetros</t>
         </is>
       </c>
       <c r="BM28" s="23"/>
@@ -10803,56 +10699,48 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Color: Gris Oscuro | Tamaño: 500W</t>
-        </is>
-      </c>
+          <t>B0GYS43G8G</t>
+        </is>
+      </c>
+      <c r="D29" s="14"/>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>Marca: Lubluelu | Función especial: Luz UV | Tipo de filtro: Cartucho | Recomendación de superficie: Alfombra | Fuente de alimentación: Eléctrico con cable | Componentes incluidos: Rodillo de cepillo | ¿Es inalámbrico?: No | Succión máxima: 18000 Milímetros | Usos recomendados para el producto: Colchones, sofás, alfombras, ropa de cama, juguetes de peluche, pelo de mascota | Factor de forma: De mano</t>
+          <t>Marca: ALLILUYAA | Función especial: Triple filtración | Recomendación de superficie: Colchón | Componentes incluidos: Filtro lavable | ¿Es inalámbrico?: Sí | Succión máxima: 10000 Milímetros | Usos recomendados para el producto: colchones, sofás, mantas, ropa, peluches y camas para mascotas | Factor de forma: De mano | Color: Blanco | Dimensiones del producto: 10l. x 10an. x 10al. milímetros</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu</t>
+          <t>ALLILUYAA</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Lubluelu/page/6949B717-1950-436B-B468-8BFB57AEF209?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/ALILILUYAA/page/6F2D9C3F-3247-41D0-93BE-BD3270082609?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirador de ácaros 3 en 1 para colchones, 18 KPa fuerte potencia de succión, limpiador de colchones contra ácaros, polvo y alérgenos, aspiradora de mano para cama, sofá, tapicería y textiles</t>
+          <t>Aspiradora De Acaros, Aspiradora Antiacaros con Triple Filtración Y Filtro Lavable, Vibración De Alta Frecuencia, Maquina Antiacaros para Artículos Textiles como Sofás, Colchones Y Peluches</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>Fuerte succión de 18 KPa para una limpieza profunda: potente aspiradora elimina instantáneamente el polvo, la suciedad y los ácaros del polvo de los colchones, sofás, alfombras, ropa de cama y peluches. Proporciona una limpieza profunda en cada esquina.
-Limpieza profunda multietapa de ácaros y alérgenos: combinación de rodillo de cepillo, vibración ultrasónica y calentamiento a alta temperatura, elimina eficazmente los ácaros y alérgenos profundamente en los tejidos, dejando un hogar fresco e higiénico.
-Limpieza hipoalergénica y suave: diseñada para hogares sensibles, la limpieza profunda se basa en tecnología mecánica de golpes y calor en lugar de aditivos químicos. Ideal para personas alérgicas, habitaciones infantiles y familias con mascotas, mientras que los textiles y las superficies se cuidan de manera cuidadosa con el material.
-Versátil para diferentes superficies y usos: adecuado para colchones, sofás, alfombras, ropa de cama y juguetes de peluche. Disuelve el polvo y las partículas de tejidos profundos y ayuda a mantener las zonas de vida muy utilizadas. Ideal para dormitorios, salas de estar y hogares con mascotas, para un hogar higiénico.
-Práctico y fácil de usar en el día a día: cable extralargo de 4 m para un mayor alcance, diseño compacto y ligero para un manejo flexible para la limpieza de colchones y muebles tapizados, así como un mantenimiento sencillo. El depósito de polvo se puede vaciar rápidamente y dejar que el filtro se seque al aire después de la limpieza.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0G4RSJQVT?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GYS43G8G?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31Nn49TeoxL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0HJRMXSZC</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -10866,7 +10754,7 @@
         </is>
       </c>
       <c r="O29" s="15">
-        <v>1050716</v>
+        <v>647557</v>
       </c>
       <c r="P29" s="15"/>
       <c r="Q29" s="16">
@@ -10879,7 +10767,7 @@
       </c>
       <c r="S29" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T29" s="15"/>
@@ -10895,11 +10783,11 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="19">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AE29" s="15"/>
       <c r="AF29" s="21">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -10946,7 +10834,7 @@
       <c r="BK29" s="23"/>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>26,5l. x 25,5an. x 33,5al. centímetros</t>
+          <t>10l. x 10an. x 10al. milímetros</t>
         </is>
       </c>
       <c r="BM29" s="23"/>
@@ -10963,48 +10851,52 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Marca: ALLILUYAA | Función especial: Triple filtración | Recomendación de superficie: Colchón | Componentes incluidos: Filtro lavable | ¿Es inalámbrico?: Sí | Succión máxima: 10000 Milímetros | Usos recomendados para el producto: colchones, sofás, mantas, ropa, peluches y camas para mascotas | Factor de forma: De mano | Color: Blanco | Dimensiones del producto: 10l. x 10an. x 10al. milímetros</t>
+          <t>Marca: Bcuuozeeing | Función especial: Ahorro de energía, Compacto, Filtro lavable, Regulación de potencia de succión sin niveles, Sin bolsa | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Ropa de cama, sofá, manta, suelo duro, alfombra | Fuente de alimentación: Funciona con red | Componentes incluidos: Aspiradora | ¿Es inalámbrico?: Sí | Vataje: 60 vatios | Tiempo de carga: 1,5 Horas | Longitud de la manguera: 1 Metros</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>ALLILUYAA</t>
+          <t>Bcuuozeeing</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/ALILILUYAA/page/6F2D9C3F-3247-41D0-93BE-BD3270082609?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora De Acaros, Aspiradora Antiacaros con Triple Filtración Y Filtro Lavable, Vibración De Alta Frecuencia, Maquina Antiacaros para Artículos Textiles como Sofás, Colchones Y Peluches</t>
+          <t>Aspirador de colchón recargable inalámbrico portátil para camas sofás</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Aspirador de ácaros de mano silencioso con control inteligente de funciones: portátil para todo el hogar. La aspiradora inalámbrica recargable es perfecta para colchones, ropa de cama y sofás de tela.
+Equipado con un rodillo de golpeo y una fuerte succión para una limpieza profunda e higiénica. Elimina eficazmente la suciedad profunda de los tejidos y la aspira inmediatamente.
+Eliminación fiable de ácaros, bacterias y polvo doméstico: ideal para personas alérgicas para crear un ambiente saludable y sin polvo.
+Diseño de carga inalámbrica sin molestos cables de alimentación, tamaño compacto y portátil para un fácil manejo. El funcionamiento silencioso no le molesta ni durante la limpieza ni en el hogar.
+Limpiador de colchones versátil para todas las superficies textiles: colchones, camas, cojines, sofás y cortinas. Un dispositivo práctico para la limpieza diaria del hogar.</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GYS43G8G?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31Nn49TeoxL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41ei98pWxqL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -11018,7 +10910,7 @@
         </is>
       </c>
       <c r="O30" s="15">
-        <v>647557</v>
+        <v>216616</v>
       </c>
       <c r="P30" s="15"/>
       <c r="Q30" s="16">
@@ -11031,7 +10923,7 @@
       </c>
       <c r="S30" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T30" s="15"/>
@@ -11046,13 +10938,9 @@
       <c r="AA30" s="4"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="2"/>
-      <c r="AD30" s="19">
-        <v>2</v>
-      </c>
+      <c r="AD30" s="19"/>
       <c r="AE30" s="15"/>
-      <c r="AF30" s="21">
-        <v>1</v>
-      </c>
+      <c r="AF30" s="21"/>
       <c r="AG30" s="22">
         <v>0</v>
       </c>
@@ -11087,10 +10975,18 @@
       <c r="AZ30" s="13"/>
       <c r="BA30" s="13"/>
       <c r="BB30" s="13"/>
-      <c r="BC30" s="13"/>
+      <c r="BC30" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD30" s="13"/>
       <c r="BE30" s="13"/>
-      <c r="BF30" s="13"/>
+      <c r="BF30" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG30" s="13"/>
       <c r="BH30" s="14"/>
       <c r="BI30" s="23"/>
@@ -11098,7 +10994,7 @@
       <c r="BK30" s="23"/>
       <c r="BL30" s="23" t="inlineStr">
         <is>
-          <t>10l. x 10an. x 10al. milímetros</t>
+          <t>18l. x 10an. x 23al. centímetros</t>
         </is>
       </c>
       <c r="BM30" s="23"/>
@@ -11115,52 +11011,53 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0H8Z6R4ZK</t>
+          <t>B0HBMBNXJ1</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>Marca: Bcuuozeeing | Función especial: Ahorro de energía, Compacto, Filtro lavable, Regulación de potencia de succión sin niveles, Sin bolsa | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Ropa de cama, sofá, manta, suelo duro, alfombra | Fuente de alimentación: Funciona con red | Componentes incluidos: Aspiradora | ¿Es inalámbrico?: Sí | Vataje: 60 vatios | Tiempo de carga: 1,5 Horas | Longitud de la manguera: 1 Metros</t>
+          <t>Marca: RANJIMA | Función especial: Luz UV | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Tapicería | Fuente de alimentación: Batería | Componentes incluidos: 1 cable de carga, 1 limpiador al vacío, 1 × Manual de instrucciones | ¿Es inalámbrico?: Sí | Capacidad: 200 ml | Usos recomendados para el producto: Cama, Pelo de mascota | Factor de forma: De mano</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Bcuuozeeing</t>
+          <t>RANJIMA</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=RANJIMA</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de colchón recargable inalámbrico portátil para camas sofás</t>
+          <t>Aspirador de ácaros para colchón, recargable, con luz UV</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de ácaros de mano silencioso con control inteligente de funciones: portátil para todo el hogar. La aspiradora inalámbrica recargable es perfecta para colchones, ropa de cama y sofás de tela.
-Equipado con un rodillo de golpeo y una fuerte succión para una limpieza profunda e higiénica. Elimina eficazmente la suciedad profunda de los tejidos y la aspira inmediatamente.
-Eliminación fiable de ácaros, bacterias y polvo doméstico: ideal para personas alérgicas para crear un ambiente saludable y sin polvo.
-Diseño de carga inalámbrica sin molestos cables de alimentación, tamaño compacto y portátil para un fácil manejo. El funcionamiento silencioso no le molesta ni durante la limpieza ni en el hogar.
-Limpiador de colchones versátil para todas las superficies textiles: colchones, camas, cojines, sofás y cortinas. Un dispositivo práctico para la limpieza diaria del hogar.</t>
+          <t>【Combinación triple contra alérgenos】Con solo pulsar un botón, activa simultáneamente tres funciones de limpieza: golpeo intenso, succión fuerte y luz germicida UV-C. Nuestro limpiador de colchones elimina eficazmente hasta el 99,9 % de los ácaros del polvo y las bacterias, así como los desencadenantes de alergias visibles e invisibles como el pelo de las mascotas y el polvo doméstico. Simplemente enciéndalo, pase por la superficie y disfrute de una tapicería higiénica y limpia, la solución ideal para colchones, sofás y otros tejidos que necesitan una limpieza rápida y profunda.
+Potente sistema de succión de 10 kPa: gracias a una potencia de succión de 10 kPa, el aspirador de colchón elimina de forma fiable el polvo, las micropartículas y los residuos de superficies delicadas como camas, colchones, tapicería y alfombras. Así se garantiza una limpieza profunda en cada uso. Por favor, utilice el dispositivo limpiador de ácaros exclusivamente en superficies textiles suaves y no en suelos duros o mesas.
+【Inalámbrico y portátil gracias a la batería】La batería recargable permite hasta una hora de tiempo de funcionamiento después de una carga completa. Sin cables molestos, el aspirador antiácaros ofrece la máxima flexibilidad de forma inalámbrica, ya sea en casa, en viajes o en el camping. La práctica carga USB-C lo convierte en el compañero perfecto para viajar y permite una limpieza espontánea de cualquier superficie de tapicería.
+Práctico recipiente de recogida lavable: el depósito de polvo de gran volumen con sistema de filtro multietapa evita obstrucciones y asegura una potencia de succión constante. Tanto el filtro HEPA extraíble como el recipiente se pueden limpiar fácilmente con agua corriente. De este modo, el rendimiento sigue siendo alto y una limpieza regular es posible sin esfuerzo. Importante: siempre deje que el filtro se seque completamente antes de su próximo uso.
+【Silencioso en el uso】La aspiradora antiácaros funciona muy silenciosamente, por lo que se puede utilizar incluso en tiempos de descanso o por la noche sin molestar a los demás. Ideal para hogares en los que se valora un ambiente tranquilo, ya sea mientras duermes, estudias o te relajas.
+Versátil para superficies textiles: ya sea colchones, sofás, alfombras, almohadas, cunas o esterillas deportivas, la aspiradora para colchón es adecuada para todas las superficies de tela del hogar. El manejo inalámbrico te permite llegar a lugares de difícil acceso sin esfuerzo. Cree un entorno de vida limpio y sin alérgenos con este ayudante confiable.</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HBMBNXJ1?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41ei98pWxqL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31DuAHlA2DL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0H8Z6R4ZK</t>
+          <t>B0HBMBNXJ1</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -11174,7 +11071,7 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>216616</v>
+        <v>84052</v>
       </c>
       <c r="P31" s="15"/>
       <c r="Q31" s="16">
@@ -11187,7 +11084,7 @@
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T31" s="15"/>
@@ -11239,18 +11136,10 @@
       <c r="AZ31" s="13"/>
       <c r="BA31" s="13"/>
       <c r="BB31" s="13"/>
-      <c r="BC31" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC31" s="13"/>
       <c r="BD31" s="13"/>
       <c r="BE31" s="13"/>
-      <c r="BF31" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF31" s="13"/>
       <c r="BG31" s="13"/>
       <c r="BH31" s="14"/>
       <c r="BI31" s="23"/>
@@ -11258,7 +11147,7 @@
       <c r="BK31" s="23"/>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>18l. x 10an. x 23al. centímetros</t>
+          <t>25l. x 20an. x 11al. centímetros</t>
         </is>
       </c>
       <c r="BM31" s="23"/>
@@ -11267,159 +11156,6 @@
       <c r="BP31" s="23"/>
       <c r="BQ31" s="23"/>
       <c r="BR31" s="13"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13">
-        <v>31</v>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>B0HBMBNXJ1</t>
-        </is>
-      </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Marca: RANJIMA | Función especial: Luz UV | Tipo de filtro: Filtro HEPA | Recomendación de superficie: Tapicería | Fuente de alimentación: Batería | Componentes incluidos: 1 cable de carga, 1 limpiador al vacío, 1 × Manual de instrucciones | ¿Es inalámbrico?: Sí | Capacidad: 200 ml | Usos recomendados para el producto: Cama, Pelo de mascota | Factor de forma: De mano</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>RANJIMA</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=RANJIMA</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>Aspirador de ácaros para colchón, recargable, con luz UV</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>【Combinación triple contra alérgenos】Con solo pulsar un botón, activa simultáneamente tres funciones de limpieza: golpeo intenso, succión fuerte y luz germicida UV-C. Nuestro limpiador de colchones elimina eficazmente hasta el 99,9 % de los ácaros del polvo y las bacterias, así como los desencadenantes de alergias visibles e invisibles como el pelo de las mascotas y el polvo doméstico. Simplemente enciéndalo, pase por la superficie y disfrute de una tapicería higiénica y limpia, la solución ideal para colchones, sofás y otros tejidos que necesitan una limpieza rápida y profunda.
-Potente sistema de succión de 10 kPa: gracias a una potencia de succión de 10 kPa, el aspirador de colchón elimina de forma fiable el polvo, las micropartículas y los residuos de superficies delicadas como camas, colchones, tapicería y alfombras. Así se garantiza una limpieza profunda en cada uso. Por favor, utilice el dispositivo limpiador de ácaros exclusivamente en superficies textiles suaves y no en suelos duros o mesas.
-【Inalámbrico y portátil gracias a la batería】La batería recargable permite hasta una hora de tiempo de funcionamiento después de una carga completa. Sin cables molestos, el aspirador antiácaros ofrece la máxima flexibilidad de forma inalámbrica, ya sea en casa, en viajes o en el camping. La práctica carga USB-C lo convierte en el compañero perfecto para viajar y permite una limpieza espontánea de cualquier superficie de tapicería.
-Práctico recipiente de recogida lavable: el depósito de polvo de gran volumen con sistema de filtro multietapa evita obstrucciones y asegura una potencia de succión constante. Tanto el filtro HEPA extraíble como el recipiente se pueden limpiar fácilmente con agua corriente. De este modo, el rendimiento sigue siendo alto y una limpieza regular es posible sin esfuerzo. Importante: siempre deje que el filtro se seque completamente antes de su próximo uso.
-【Silencioso en el uso】La aspiradora antiácaros funciona muy silenciosamente, por lo que se puede utilizar incluso en tiempos de descanso o por la noche sin molestar a los demás. Ideal para hogares en los que se valora un ambiente tranquilo, ya sea mientras duermes, estudias o te relajas.
-Versátil para superficies textiles: ya sea colchones, sofás, alfombras, almohadas, cunas o esterillas deportivas, la aspiradora para colchón es adecuada para todas las superficies de tela del hogar. El manejo inalámbrico te permite llegar a lugares de difícil acceso sin esfuerzo. Cree un entorno de vida limpio y sin alérgenos con este ayudante confiable.</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0HBMBNXJ1?psc=1</t>
-        </is>
-      </c>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31DuAHlA2DL._AC_US200_.jpg</t>
-        </is>
-      </c>
-      <c r="L32" s="14" t="inlineStr">
-        <is>
-          <t>B0HBMBNXJ1</t>
-        </is>
-      </c>
-      <c r="M32" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras de futones</t>
-        </is>
-      </c>
-      <c r="N32" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O32" s="15">
-        <v>84052</v>
-      </c>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="16">
-        <v>0</v>
-      </c>
-      <c r="R32" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras de futones</t>
-        </is>
-      </c>
-      <c r="S32" s="18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T32" s="15"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="15"/>
-      <c r="W32" s="15"/>
-      <c r="X32" s="15"/>
-      <c r="Y32" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="4"/>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="2"/>
-      <c r="AD32" s="19"/>
-      <c r="AE32" s="15"/>
-      <c r="AF32" s="21"/>
-      <c r="AG32" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="20"/>
-      <c r="AI32" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ32"/>
-      <c r="AK32" s="13"/>
-      <c r="AL32" s="19"/>
-      <c r="AM32" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN32" s="13"/>
-      <c r="AO32" s="13"/>
-      <c r="AP32" s="20"/>
-      <c r="AQ32" s="19"/>
-      <c r="AR32" s="19"/>
-      <c r="AS32" s="14"/>
-      <c r="AT32" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU32" s="13"/>
-      <c r="AV32" s="14"/>
-      <c r="AW32" s="13"/>
-      <c r="AX32" s="13"/>
-      <c r="AY32" s="13"/>
-      <c r="AZ32" s="13"/>
-      <c r="BA32" s="13"/>
-      <c r="BB32" s="13"/>
-      <c r="BC32" s="13"/>
-      <c r="BD32" s="13"/>
-      <c r="BE32" s="13"/>
-      <c r="BF32" s="13"/>
-      <c r="BG32" s="13"/>
-      <c r="BH32" s="14"/>
-      <c r="BI32" s="23"/>
-      <c r="BJ32" s="23"/>
-      <c r="BK32" s="23"/>
-      <c r="BL32" s="23" t="inlineStr">
-        <is>
-          <t>25l. x 20an. x 11al. centímetros</t>
-        </is>
-      </c>
-      <c r="BM32" s="23"/>
-      <c r="BN32" s="23"/>
-      <c r="BO32" s="23"/>
-      <c r="BP32" s="23"/>
-      <c r="BQ32" s="23"/>
-      <c r="BR32" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11583,85 +11319,77 @@
     <hyperlink ref="M22" r:id="rId156" tooltip="https://www.amazon.es/b?node=13713592031"/>
     <hyperlink ref="N22" r:id="rId157"/>
     <hyperlink ref="AW22" r:id="rId158" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3MSJ66TMU8M67"/>
-    <hyperlink ref="C23" r:id="rId159" tooltip="https://www.amazon.es/dp/B0FBX24WH6"/>
-    <hyperlink ref="G23" r:id="rId160" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=syayw"/>
-    <hyperlink ref="J23" r:id="rId161" tooltip="https://www.amazon.es/dp/B0FBX24WH6?psc=1"/>
-    <hyperlink ref="K23" r:id="rId162" tooltip="https://images-na.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_US600_.jpg"/>
-    <hyperlink ref="L23" r:id="rId163" tooltip="https://www.amazon.es/dp/B0FQ4FRYT7"/>
-    <hyperlink ref="M23" r:id="rId164" tooltip="https://www.amazon.es/b?node=2404713031"/>
+    <hyperlink ref="C23" r:id="rId159" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
+    <hyperlink ref="G23" r:id="rId160" tooltip="https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J23" r:id="rId161" tooltip="https://www.amazon.es/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K23" r:id="rId162" tooltip="https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId163" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
+    <hyperlink ref="M23" r:id="rId164" tooltip="https://www.amazon.es/b?node=13713592031"/>
     <hyperlink ref="N23" r:id="rId165"/>
-    <hyperlink ref="AW23" r:id="rId166" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3T9BSXCSWI46M"/>
-    <hyperlink ref="C24" r:id="rId167" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
-    <hyperlink ref="G24" r:id="rId168" tooltip="https://www.amazon.es/stores/JIGOO-ES/page/23E9C8F3-B11D-41BE-B25B-391D7999E178?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J24" r:id="rId169" tooltip="https://www.amazon.es/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K24" r:id="rId170" tooltip="https://m.media-amazon.com/images/I/31va0mFb48L._AC_US200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId171" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
-    <hyperlink ref="M24" r:id="rId172" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N24" r:id="rId173"/>
-    <hyperlink ref="C25" r:id="rId174" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
-    <hyperlink ref="G25" r:id="rId175" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J25" r:id="rId176" tooltip="https://www.amazon.es/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K25" r:id="rId177" tooltip="https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId178" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
-    <hyperlink ref="M25" r:id="rId179" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N25" r:id="rId180"/>
-    <hyperlink ref="C26" r:id="rId181" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
-    <hyperlink ref="G26" r:id="rId182" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
-    <hyperlink ref="J26" r:id="rId183" tooltip="https://www.amazon.es/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K26" r:id="rId184" tooltip="https://m.media-amazon.com/images/I/41B+I610d+L._AC_US200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId185" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
-    <hyperlink ref="M26" r:id="rId186" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N26" r:id="rId187"/>
-    <hyperlink ref="C27" r:id="rId188" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
-    <hyperlink ref="G27" r:id="rId189" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J27" r:id="rId190" tooltip="https://www.amazon.es/dp/B0FVS559GZ?psc=1"/>
-    <hyperlink ref="K27" r:id="rId191" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId192" tooltip="https://www.amazon.es/dp/B0GHDFVK7R"/>
-    <hyperlink ref="M27" r:id="rId193" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N27" r:id="rId194"/>
-    <hyperlink ref="C28" r:id="rId195" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
-    <hyperlink ref="G28" r:id="rId196" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J28" r:id="rId197" tooltip="https://www.amazon.es/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K28" r:id="rId198" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId199" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
-    <hyperlink ref="M28" r:id="rId200" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N28" r:id="rId201"/>
-    <hyperlink ref="C29" r:id="rId202" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
-    <hyperlink ref="G29" r:id="rId203" tooltip="https://www.amazon.es/stores/Lubluelu/page/6949B717-1950-436B-B468-8BFB57AEF209?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J29" r:id="rId204" tooltip="https://www.amazon.es/dp/B0G4RSJQVT?psc=1"/>
-    <hyperlink ref="K29" r:id="rId205" tooltip="https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId206" tooltip="https://www.amazon.es/dp/B0HJRMXSZC"/>
-    <hyperlink ref="M29" r:id="rId207" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N29" r:id="rId208"/>
-    <hyperlink ref="C30" r:id="rId209" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
-    <hyperlink ref="G30" r:id="rId210" tooltip="https://www.amazon.es/stores/ALILILUYAA/page/6F2D9C3F-3247-41D0-93BE-BD3270082609?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J30" r:id="rId211" tooltip="https://www.amazon.es/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K30" r:id="rId212" tooltip="https://m.media-amazon.com/images/I/31Nn49TeoxL._AC_US200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId213" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
-    <hyperlink ref="M30" r:id="rId214" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N30" r:id="rId215"/>
-    <hyperlink ref="C31" r:id="rId216" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="G31" r:id="rId217" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing"/>
-    <hyperlink ref="J31" r:id="rId218" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1"/>
-    <hyperlink ref="K31" r:id="rId219" tooltip="https://m.media-amazon.com/images/I/41ei98pWxqL._AC_US200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId220" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="M31" r:id="rId221" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N31" r:id="rId222"/>
-    <hyperlink ref="C32" r:id="rId223" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
-    <hyperlink ref="G32" r:id="rId224" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=RANJIMA"/>
-    <hyperlink ref="J32" r:id="rId225" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1?psc=1"/>
-    <hyperlink ref="K32" r:id="rId226" tooltip="https://m.media-amazon.com/images/I/31DuAHlA2DL._AC_US200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId227" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
-    <hyperlink ref="M32" r:id="rId228" tooltip="https://www.amazon.es/b?node=13713592031"/>
-    <hyperlink ref="N32" r:id="rId229"/>
+    <hyperlink ref="C24" r:id="rId166" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
+    <hyperlink ref="G24" r:id="rId167" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J24" r:id="rId168" tooltip="https://www.amazon.es/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K24" r:id="rId169" tooltip="https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId170" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
+    <hyperlink ref="M24" r:id="rId171" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N24" r:id="rId172"/>
+    <hyperlink ref="C25" r:id="rId173" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
+    <hyperlink ref="G25" r:id="rId174" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
+    <hyperlink ref="J25" r:id="rId175" tooltip="https://www.amazon.es/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K25" r:id="rId176" tooltip="https://m.media-amazon.com/images/I/41B+I610d+L._AC_US200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId177" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
+    <hyperlink ref="M25" r:id="rId178" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N25" r:id="rId179"/>
+    <hyperlink ref="C26" r:id="rId180" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
+    <hyperlink ref="G26" r:id="rId181" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J26" r:id="rId182" tooltip="https://www.amazon.es/dp/B0FVS559GZ?psc=1"/>
+    <hyperlink ref="K26" r:id="rId183" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId184" tooltip="https://www.amazon.es/dp/B0GHDFVK7R"/>
+    <hyperlink ref="M26" r:id="rId185" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N26" r:id="rId186"/>
+    <hyperlink ref="C27" r:id="rId187" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
+    <hyperlink ref="G27" r:id="rId188" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J27" r:id="rId189" tooltip="https://www.amazon.es/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K27" r:id="rId190" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId191" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
+    <hyperlink ref="M27" r:id="rId192" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N27" r:id="rId193"/>
+    <hyperlink ref="C28" r:id="rId194" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
+    <hyperlink ref="G28" r:id="rId195" tooltip="https://www.amazon.es/stores/Lubluelu/page/6949B717-1950-436B-B468-8BFB57AEF209?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J28" r:id="rId196" tooltip="https://www.amazon.es/dp/B0G4RSJQVT?psc=1"/>
+    <hyperlink ref="K28" r:id="rId197" tooltip="https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId198" tooltip="https://www.amazon.es/dp/B0HJRMXSZC"/>
+    <hyperlink ref="M28" r:id="rId199" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N28" r:id="rId200"/>
+    <hyperlink ref="C29" r:id="rId201" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
+    <hyperlink ref="G29" r:id="rId202" tooltip="https://www.amazon.es/stores/ALILILUYAA/page/6F2D9C3F-3247-41D0-93BE-BD3270082609?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J29" r:id="rId203" tooltip="https://www.amazon.es/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K29" r:id="rId204" tooltip="https://m.media-amazon.com/images/I/31Nn49TeoxL._AC_US200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId205" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
+    <hyperlink ref="M29" r:id="rId206" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N29" r:id="rId207"/>
+    <hyperlink ref="C30" r:id="rId208" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="G30" r:id="rId209" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Bcuuozeeing"/>
+    <hyperlink ref="J30" r:id="rId210" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1"/>
+    <hyperlink ref="K30" r:id="rId211" tooltip="https://m.media-amazon.com/images/I/41ei98pWxqL._AC_US200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId212" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="M30" r:id="rId213" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N30" r:id="rId214"/>
+    <hyperlink ref="C31" r:id="rId215" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
+    <hyperlink ref="G31" r:id="rId216" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=RANJIMA"/>
+    <hyperlink ref="J31" r:id="rId217" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1?psc=1"/>
+    <hyperlink ref="K31" r:id="rId218" tooltip="https://m.media-amazon.com/images/I/31DuAHlA2DL._AC_US200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId219" tooltip="https://www.amazon.es/dp/B0HBMBNXJ1"/>
+    <hyperlink ref="M31" r:id="rId220" tooltip="https://www.amazon.es/b?node=13713592031"/>
+    <hyperlink ref="N31" r:id="rId221"/>
   </hyperlinks>
-  <drawing r:id="rId230"/>
+  <drawing r:id="rId222"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -12105,25 +11833,6 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>syayw</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <v>0</v>
-      </c>
-      <c r="C22" s="15">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -12132,7 +11841,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -12440,25 +12149,6 @@
       <c r="E14" s="15"/>
       <c r="F14" s="20"/>
       <c r="G14" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>nousaeg</t>
-        </is>
-      </c>
-      <c r="B15" s="15">
-        <v>0</v>
-      </c>
-      <c r="C15" s="15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="22">
         <v>0.0</v>
       </c>
     </row>
